--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.07065910905233</v>
+        <v>3.911482105221004</v>
       </c>
       <c r="D2" t="n">
-        <v>21.18876035388732</v>
+        <v>3.44317355750669</v>
       </c>
       <c r="E2" t="n">
-        <v>19.9943763899688</v>
+        <v>3.24908616336993</v>
       </c>
       <c r="F2" t="n">
-        <v>19.47066419197106</v>
+        <v>3.163982931195297</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.27956019631543</v>
+        <v>10.93292853190126</v>
       </c>
       <c r="D3" t="n">
-        <v>22.01056229649096</v>
+        <v>3.576716373179781</v>
       </c>
       <c r="E3" t="n">
-        <v>19.9943763899688</v>
+        <v>3.24908616336993</v>
       </c>
       <c r="F3" t="n">
-        <v>19.47066419197106</v>
+        <v>3.163982931195297</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.64336051824978</v>
+        <v>10.66704608421559</v>
       </c>
       <c r="D4" t="n">
-        <v>62.89704525588888</v>
+        <v>10.22076985408194</v>
       </c>
       <c r="E4" t="n">
-        <v>19.9943763899688</v>
+        <v>3.24908616336993</v>
       </c>
       <c r="F4" t="n">
-        <v>19.47066419197106</v>
+        <v>3.163982931195297</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
